--- a/lesson-1-8-bootstrap/bakery_customers.xlsx
+++ b/lesson-1-8-bootstrap/bakery_customers.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9DE360-E42A-7E42-99BD-179883D5C4B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17920" activeTab="1" xr2:uid="{B789D35D-8286-0147-8D32-7509A9EA0EA4}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17900" activeTab="1" xr2:uid="{B789D35D-8286-0147-8D32-7509A9EA0EA4}"/>
   </bookViews>
   <sheets>
     <sheet name="bakery_customers" sheetId="1" r:id="rId1"/>
